--- a/artfynd/A 20169-2022 artfynd.xlsx
+++ b/artfynd/A 20169-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 20169-2022 artfynd.xlsx
+++ b/artfynd/A 20169-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>87490510</v>
+        <v>119202342</v>
       </c>
       <c r="B2" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95962</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1312</v>
+        <v>2387</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Källpraktmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Pseudobryum cinclidioides</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Huebener) T.J.Kop.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>NO Åkersjön, Jmt</t>
+          <t>Gastflon, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>457236.9016073089</v>
+        <v>456535</v>
       </c>
       <c r="R2" t="n">
-        <v>7073241.216702867</v>
+        <v>7073804</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -769,72 +754,66 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
-      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>87490492</v>
+        <v>119202395</v>
       </c>
       <c r="B3" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>75300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6440</v>
+        <v>6428</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>NO Åkersjön, Jmt</t>
+          <t>Gastflon, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>457251.8243759467</v>
+        <v>456587</v>
       </c>
       <c r="R3" t="n">
-        <v>7073264.010519184</v>
+        <v>7073798</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -858,22 +837,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -888,65 +857,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tore Dahlberg</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>87485590</v>
+        <v>119202404</v>
       </c>
       <c r="B4" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6462</v>
+        <v>6440</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>NO Åkersjön, Jmt</t>
+          <t>Gastflon, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>457080.1751066805</v>
+        <v>456589</v>
       </c>
       <c r="R4" t="n">
-        <v>7073341.08406708</v>
+        <v>7073807</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -970,22 +934,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1000,27 +954,22 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Vera Ranow</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Vera Ranow, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Tove Lönneborg</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>87485594</v>
+        <v>119202325</v>
       </c>
       <c r="B5" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1028,37 +977,37 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221952</v>
+        <v>6462</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>NO Åkersjön, Jmt</t>
+          <t>Gastflon, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>457289.1307246009</v>
+        <v>456614</v>
       </c>
       <c r="R5" t="n">
-        <v>7073174.17049535</v>
+        <v>7073801</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1082,22 +1031,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1112,65 +1051,60 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Vera Ranow</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Vera Ranow, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Tove Lönneborg</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>87490390</v>
+        <v>119202347</v>
       </c>
       <c r="B6" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83305</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>6486</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Skuggnål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Chaenotheca sphaerocephala</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>Nádv.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>NO Åkersjön, Jmt</t>
+          <t>Gastflon, Jmt</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>457359.8702084666</v>
+        <v>456588</v>
       </c>
       <c r="R6" t="n">
-        <v>7073231.145827378</v>
+        <v>7073808</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1194,22 +1128,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-08-07</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1224,27 +1148,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Elin Lönnberg</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Elin Lönnberg, Karl Soler Kinnerbäck, Vera Ranow, Iris Elmér, Tove Lönneborg, Tore Dahlberg</t>
+          <t>Jesper Wadstein</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>87490382</v>
+        <v>87485600</v>
       </c>
       <c r="B7" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1252,42 +1171,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>NO Åkersjön, Jmt</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>457220.1034069693</v>
+        <v>457271</v>
       </c>
       <c r="R7" t="n">
-        <v>7073275.939698027</v>
+        <v>7073311</v>
       </c>
       <c r="S7" t="n">
         <v>20</v>
@@ -1317,19 +1228,9 @@
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,27 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Elin Lönnberg</t>
+          <t>Vera Ranow</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Elin Lönnberg, Karl Soler Kinnerbäck, Vera Ranow, Iris Elmér, Tove Lönneborg, Tore Dahlberg</t>
+          <t>Vera Ranow, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Tove Lönneborg</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>87486990</v>
+        <v>87490392</v>
       </c>
       <c r="B8" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1372,42 +1268,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Nordöstra Åkersjön, Jmt</t>
+          <t>NO Åkersjön, Jmt</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>457237.2139833089</v>
+        <v>457195</v>
       </c>
       <c r="R8" t="n">
-        <v>7073264.208984059</v>
+        <v>7073273</v>
       </c>
       <c r="S8" t="n">
         <v>20</v>
@@ -1437,54 +1328,40 @@
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tove Lönneborg</t>
+          <t>Elin Lönnberg</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tove Lönneborg, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Vera Ranow</t>
+          <t>Elin Lönnberg, Karl Soler Kinnerbäck, Vera Ranow, Iris Elmér, Tove Lönneborg, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>87490389</v>
+        <v>87490510</v>
       </c>
       <c r="B9" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1492,21 +1369,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1516,10 +1393,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>457254.9263452531</v>
+        <v>457237</v>
       </c>
       <c r="R9" t="n">
-        <v>7073198.958557333</v>
+        <v>7073241</v>
       </c>
       <c r="S9" t="n">
         <v>20</v>
@@ -1549,54 +1426,40 @@
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Elin Lönnberg</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Elin Lönnberg, Karl Soler Kinnerbäck, Vera Ranow, Iris Elmér, Tove Lönneborg, Tore Dahlberg</t>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>87485600</v>
+        <v>87490511</v>
       </c>
       <c r="B10" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>457271.0616912641</v>
+        <v>457339</v>
       </c>
       <c r="R10" t="n">
-        <v>7073311.068543888</v>
+        <v>7073157</v>
       </c>
       <c r="S10" t="n">
         <v>20</v>
@@ -1661,76 +1524,62 @@
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Vera Ranow</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Vera Ranow, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Tove Lönneborg</t>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>87485593</v>
+        <v>87490512</v>
       </c>
       <c r="B11" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1740,10 +1589,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>457059.1979688552</v>
+        <v>457408</v>
       </c>
       <c r="R11" t="n">
-        <v>7073328.987748293</v>
+        <v>7073212</v>
       </c>
       <c r="S11" t="n">
         <v>20</v>
@@ -1773,76 +1622,62 @@
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD11" t="b">
         <v>0</v>
       </c>
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Vera Ranow</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Vera Ranow, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Tove Lönneborg</t>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>87485592</v>
+        <v>87490514</v>
       </c>
       <c r="B12" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1852,10 +1687,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>457059.1979688552</v>
+        <v>457393</v>
       </c>
       <c r="R12" t="n">
-        <v>7073328.987748293</v>
+        <v>7073198</v>
       </c>
       <c r="S12" t="n">
         <v>20</v>
@@ -1885,54 +1720,40 @@
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Vera Ranow</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Vera Ranow, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Tove Lönneborg</t>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>87490388</v>
+        <v>87502885</v>
       </c>
       <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1940,21 +1761,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5432</v>
+        <v>1312</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1964,10 +1785,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>457220.1034069693</v>
+        <v>457227</v>
       </c>
       <c r="R13" t="n">
-        <v>7073275.939698027</v>
+        <v>7073239</v>
       </c>
       <c r="S13" t="n">
         <v>20</v>
@@ -1997,19 +1818,9 @@
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2024,49 +1835,44 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Elin Lönnberg</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Elin Lönnberg, Karl Soler Kinnerbäck, Vera Ranow, Iris Elmér, Tove Lönneborg, Tore Dahlberg</t>
+          <t>Karl Soler Kinnerbäck, Tore Dahlberg, Elin Lönnberg, Vera Ranow, Tove Lönneborg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>87485591</v>
+        <v>87502891</v>
       </c>
       <c r="B14" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6463</v>
+        <v>1312</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2076,10 +1882,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>457080.1751066805</v>
+        <v>457321</v>
       </c>
       <c r="R14" t="n">
-        <v>7073341.08406708</v>
+        <v>7073218</v>
       </c>
       <c r="S14" t="n">
         <v>20</v>
@@ -2109,19 +1915,9 @@
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2136,27 +1932,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Vera Ranow</t>
+          <t>Karl Soler Kinnerbäck</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Vera Ranow, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Tove Lönneborg</t>
+          <t>Karl Soler Kinnerbäck, Tore Dahlberg, Elin Lönnberg, Vera Ranow, Tove Lönneborg, Iris Elmér</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>87502891</v>
+        <v>87502892</v>
       </c>
       <c r="B15" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2188,10 +1979,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>457321.1656471983</v>
+        <v>457237</v>
       </c>
       <c r="R15" t="n">
-        <v>7073217.960818846</v>
+        <v>7073196</v>
       </c>
       <c r="S15" t="n">
         <v>20</v>
@@ -2221,19 +2012,9 @@
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,15 +2041,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>87502886</v>
+        <v>87490381</v>
       </c>
       <c r="B16" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2300,10 +2076,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>457227.1312316963</v>
+        <v>457195</v>
       </c>
       <c r="R16" t="n">
-        <v>7073239.13824617</v>
+        <v>7073273</v>
       </c>
       <c r="S16" t="n">
         <v>20</v>
@@ -2333,19 +2109,9 @@
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2360,27 +2126,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Elin Lönnberg</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Tore Dahlberg, Elin Lönnberg, Vera Ranow, Tove Lönneborg, Iris Elmér</t>
+          <t>Elin Lönnberg, Karl Soler Kinnerbäck, Vera Ranow, Iris Elmér, Tove Lönneborg, Tore Dahlberg</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>87502892</v>
+        <v>87490492</v>
       </c>
       <c r="B17" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2388,21 +2149,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2412,10 +2173,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>457237.174362248</v>
+        <v>457252</v>
       </c>
       <c r="R17" t="n">
-        <v>7073196.103942099</v>
+        <v>7073264</v>
       </c>
       <c r="S17" t="n">
         <v>20</v>
@@ -2445,19 +2206,9 @@
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2472,27 +2223,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck</t>
+          <t>Tore Dahlberg</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Karl Soler Kinnerbäck, Tore Dahlberg, Elin Lönnberg, Vera Ranow, Tove Lönneborg, Iris Elmér</t>
+          <t>Tore Dahlberg, Karl Soler Kinnerbäck, Tove Lönneborg, Vera Ranow</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>87502885</v>
+        <v>87502886</v>
       </c>
       <c r="B18" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2500,21 +2246,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1312</v>
+        <v>6440</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2524,10 +2270,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>457227.1312316963</v>
+        <v>457227</v>
       </c>
       <c r="R18" t="n">
-        <v>7073239.13824617</v>
+        <v>7073239</v>
       </c>
       <c r="S18" t="n">
         <v>20</v>
@@ -2557,19 +2303,9 @@
           <t>2020-08-15</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2020-08-15</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2593,6 +2329,701 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>87485590</v>
+      </c>
+      <c r="B19" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>NO Åkersjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>457080</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7073341</v>
+      </c>
+      <c r="S19" t="n">
+        <v>20</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Vera Ranow</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Vera Ranow, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Tove Lönneborg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>87485592</v>
+      </c>
+      <c r="B20" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>NO Åkersjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>457059</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7073329</v>
+      </c>
+      <c r="S20" t="n">
+        <v>20</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Vera Ranow</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Vera Ranow, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Tove Lönneborg</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>87485591</v>
+      </c>
+      <c r="B21" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>NO Åkersjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>457080</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7073341</v>
+      </c>
+      <c r="S21" t="n">
+        <v>20</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Vera Ranow</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Vera Ranow, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Tove Lönneborg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>87485593</v>
+      </c>
+      <c r="B22" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>NO Åkersjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>457059</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7073329</v>
+      </c>
+      <c r="S22" t="n">
+        <v>20</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Vera Ranow</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Vera Ranow, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Tove Lönneborg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>87486990</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Nordöstra Åkersjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>457237</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7073264</v>
+      </c>
+      <c r="S23" t="n">
+        <v>20</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Tove Lönneborg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Tove Lönneborg, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Vera Ranow</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>87490382</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>NO Åkersjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>457220</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7073276</v>
+      </c>
+      <c r="S24" t="n">
+        <v>20</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Elin Lönnberg, Karl Soler Kinnerbäck, Vera Ranow, Iris Elmér, Tove Lönneborg, Tore Dahlberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>87485594</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>NO Åkersjön, Jmt</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>457289</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7073174</v>
+      </c>
+      <c r="S25" t="n">
+        <v>20</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Föllinge</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2020-08-15</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Vera Ranow</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Vera Ranow, Tore Dahlberg, Karl Soler Kinnerbäck, Elin Lönnberg, Tove Lönneborg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 20169-2022 artfynd.xlsx
+++ b/artfynd/A 20169-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY25"/>
+  <dimension ref="A1:AZ25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202342</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202395</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202404</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202325</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119202347</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87485600</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1355,6 +1390,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490392</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1453,6 +1493,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490510</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1551,6 +1596,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490511</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1649,6 +1699,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490512</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490514</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502885</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502891</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502892</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490381</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490492</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87502886</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2426,6 +2516,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87485590</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2523,6 +2618,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87485592</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2620,6 +2720,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87485591</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2717,6 +2822,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87485593</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2822,6 +2932,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87486990</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2927,6 +3042,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87490382</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3024,8 +3144,39 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/87485594</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>